--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487207_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487207_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>I. SALAZAR ORTEGA</t>
+          <t>M. SAINZ DE LA MAZA GARRASTACHU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.6956</v>
+        <v>8.375400000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>7.2517</v>
+        <v>6.4291</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4439</v>
+        <v>1.9463</v>
       </c>
       <c r="G2" t="n">
-        <v>6.4085</v>
+        <v>4.0022</v>
       </c>
       <c r="H2" t="n">
-        <v>2.9341</v>
+        <v>1.5845</v>
       </c>
       <c r="I2" t="n">
-        <v>3.4744</v>
+        <v>2.4177</v>
       </c>
       <c r="J2" t="n">
-        <v>6.5153</v>
+        <v>4.4489</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8291</v>
+        <v>2.4061</v>
       </c>
       <c r="L2" t="n">
-        <v>2.6861</v>
+        <v>2.0428</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1068</v>
+        <v>-0.4468</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8951</v>
+        <v>-0.8216</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7883</v>
+        <v>0.3748</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.7371</v>
+        <v>0.193</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.8602</v>
+        <v>-1.9301</v>
       </c>
       <c r="R2" t="n">
         <v>2.1231</v>
       </c>
       <c r="S2" t="n">
-        <v>6.0242</v>
+        <v>1.7665</v>
       </c>
       <c r="T2" t="n">
-        <v>4.5966</v>
+        <v>1.4965</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4277</v>
+        <v>0.27</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>2.4137</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.4137</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. SAINZ DE LA MAZA GARRASTACHU</t>
+          <t>I. SALAZAR ORTEGA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>9.1517</v>
+        <v>7.0658</v>
       </c>
       <c r="E3" t="n">
-        <v>7.3928</v>
+        <v>4.5856</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7589</v>
+        <v>2.4802</v>
       </c>
       <c r="G3" t="n">
-        <v>4.0022</v>
+        <v>6.4085</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5845</v>
+        <v>2.9341</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4177</v>
+        <v>3.4744</v>
       </c>
       <c r="J3" t="n">
-        <v>4.4489</v>
+        <v>6.5153</v>
       </c>
       <c r="K3" t="n">
-        <v>2.4061</v>
+        <v>3.8291</v>
       </c>
       <c r="L3" t="n">
-        <v>2.0428</v>
+        <v>2.6861</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4468</v>
+        <v>-0.1068</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8216</v>
+        <v>-0.8951</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3748</v>
+        <v>0.7883</v>
       </c>
       <c r="P3" t="n">
-        <v>0.193</v>
+        <v>-1.7371</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9301</v>
+        <v>-3.8602</v>
       </c>
       <c r="R3" t="n">
         <v>2.1231</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5428</v>
+        <v>2.3944</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4602</v>
+        <v>1.9305</v>
       </c>
       <c r="U3" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.464</v>
       </c>
       <c r="V3" t="n">
-        <v>2.4137</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.4137</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.5232</v>
+        <v>5.8365</v>
       </c>
       <c r="E4" t="n">
-        <v>6.0539</v>
+        <v>6.0727</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5306999999999999</v>
+        <v>-0.2363</v>
       </c>
       <c r="G4" t="n">
         <v>5.324</v>
@@ -766,13 +766,13 @@
         <v>1.3511</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0411</v>
+        <v>1.3544</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8144</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2267</v>
+        <v>0.5212</v>
       </c>
       <c r="V4" t="n">
         <v>-1.228</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.128</v>
+        <v>5.3545</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7734</v>
+        <v>2.0534</v>
       </c>
       <c r="F5" t="n">
-        <v>3.3547</v>
+        <v>3.3011</v>
       </c>
       <c r="G5" t="n">
         <v>4.1029</v>
@@ -844,13 +844,13 @@
         <v>2.1231</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1679</v>
+        <v>1.0586</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8183</v>
+        <v>0.4617</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6504</v>
+        <v>0.5968</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5466</v>
+        <v>1.6934</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4856</v>
+        <v>2.204</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9389</v>
+        <v>-0.5106000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>3.7592</v>
@@ -922,13 +922,13 @@
         <v>1.3511</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0854</v>
+        <v>1.2321</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9333</v>
+        <v>0.6518</v>
       </c>
       <c r="U6" t="n">
-        <v>0.152</v>
+        <v>0.5803</v>
       </c>
       <c r="V6" t="n">
         <v>-3.6839</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.4694</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.5069</v>
+        <v>-1.6869</v>
       </c>
       <c r="F7" t="n">
-        <v>2.5846</v>
+        <v>2.1563</v>
       </c>
       <c r="G7" t="n">
         <v>0.2882</v>
@@ -1000,13 +1000,13 @@
         <v>1.3511</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6967</v>
+        <v>1.0883</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5354</v>
+        <v>0.2846</v>
       </c>
       <c r="U7" t="n">
-        <v>1.232</v>
+        <v>0.8037</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3281</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9929</v>
+        <v>-0.4396</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0534</v>
+        <v>0.366</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9395</v>
+        <v>-0.8056</v>
       </c>
       <c r="G8" t="n">
         <v>0.4068</v>
@@ -1078,13 +1078,13 @@
         <v>0.579</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7277</v>
+        <v>-0.1745</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4164</v>
+        <v>0.003</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3113</v>
+        <v>-0.1775</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2859</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1468</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4441</v>
+        <v>-0.2831</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7027</v>
+        <v>-0.3012</v>
       </c>
       <c r="G9" t="n">
         <v>-1.1373</v>
@@ -1156,13 +1156,13 @@
         <v>1.3511</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8467</v>
+        <v>0.7159</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4468</v>
+        <v>0.7141999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3999</v>
+        <v>0.0016</v>
       </c>
       <c r="V9" t="n">
         <v>-1.5138</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7137</v>
+        <v>-1.8342</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.9424</v>
+        <v>-4.063</v>
       </c>
       <c r="F10" t="n">
         <v>2.2288</v>
@@ -1234,10 +1234,10 @@
         <v>1.7371</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4746</v>
+        <v>0.4049</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6993</v>
+        <v>0.1801</v>
       </c>
       <c r="U10" t="n">
         <v>0.2247</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1647</v>
+        <v>-2.3447</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.9286</v>
+        <v>-4.1086</v>
       </c>
       <c r="F11" t="n">
         <v>1.7639</v>
@@ -1312,10 +1312,10 @@
         <v>1.3511</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4151</v>
+        <v>0.4049</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6398</v>
+        <v>0.1801</v>
       </c>
       <c r="U11" t="n">
         <v>0.2247</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>22.1047</v>
+        <v>23.5923</v>
       </c>
       <c r="E12" t="n">
-        <v>10.082</v>
+        <v>11.56920000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>12.023</v>
+        <v>12.0229</v>
       </c>
       <c r="G12" t="n">
         <v>16.4168</v>
@@ -1390,13 +1390,13 @@
         <v>15.4409</v>
       </c>
       <c r="S12" t="n">
-        <v>8.758199999999999</v>
+        <v>10.2455</v>
       </c>
       <c r="T12" t="n">
-        <v>5.248499999999999</v>
+        <v>6.7357</v>
       </c>
       <c r="U12" t="n">
-        <v>3.5096</v>
+        <v>3.5095</v>
       </c>
       <c r="V12" t="n">
         <v>-3.069900000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.6189</v>
+        <v>3.9329</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0837</v>
+        <v>2.1838</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5352</v>
+        <v>1.7491</v>
       </c>
       <c r="G13" t="n">
         <v>2.738</v>
@@ -1468,13 +1468,13 @@
         <v>1.3511</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.733</v>
+        <v>-0.4191</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4759</v>
+        <v>-0.3758</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2571</v>
+        <v>-0.0433</v>
       </c>
       <c r="V13" t="n">
         <v>1.228</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.2833</v>
+        <v>-0.0692</v>
       </c>
       <c r="E14" t="n">
         <v>-1.135</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8517</v>
+        <v>1.0659</v>
       </c>
       <c r="G14" t="n">
         <v>-0.2043</v>
@@ -1546,13 +1546,13 @@
         <v>1.5441</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9862</v>
+        <v>-0.772</v>
       </c>
       <c r="T14" t="n">
         <v>-0.7733</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2128</v>
+        <v>0.0013</v>
       </c>
       <c r="V14" t="n">
         <v>0.3281</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.1537</v>
+        <v>-0.8603</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9174</v>
+        <v>1.318</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.0712</v>
+        <v>-2.1782</v>
       </c>
       <c r="G15" t="n">
         <v>-0.5377999999999999</v>
@@ -1624,13 +1624,13 @@
         <v>1.158</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.546</v>
+        <v>-0.2525</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4468</v>
+        <v>-0.0462</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0992</v>
+        <v>-0.2062</v>
       </c>
       <c r="V15" t="n">
         <v>-1.228</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. NDOYE</t>
+          <t>A. GARCIA NAVALON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.9156</v>
+        <v>-2.4642</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0539</v>
+        <v>-2.7648</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.9694</v>
+        <v>0.3007</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.8154</v>
+        <v>-0.5969</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0414</v>
+        <v>-0.5662</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.774</v>
+        <v>-0.0307</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1071</v>
+        <v>-0.1834</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6933</v>
+        <v>0.3621</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5862000000000001</v>
+        <v>-0.5455</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.9225</v>
+        <v>-0.4135</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7347</v>
+        <v>-0.9283</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.1878</v>
+        <v>0.5148</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.579</v>
+        <v>-0.965</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3511</v>
+        <v>0.965</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5367</v>
+        <v>-0.9022</v>
       </c>
       <c r="T16" t="n">
-        <v>1.363</v>
+        <v>-0.6514</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8263</v>
+        <v>-0.2509</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9421</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.5138</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5717</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. GARCIA NAVALON</t>
+          <t>N. NDOYE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.1926</v>
+        <v>-2.8905</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.0653</v>
+        <v>0.0524</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1273</v>
+        <v>-2.943</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5969</v>
+        <v>-2.8154</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5662</v>
+        <v>-0.0414</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0307</v>
+        <v>-2.774</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1834</v>
+        <v>0.1071</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3621</v>
+        <v>0.6933</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5455</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4135</v>
+        <v>-2.9225</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9283</v>
+        <v>-0.7347</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5148</v>
+        <v>-2.1878</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.965</v>
+        <v>-0.579</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R17" t="n">
-        <v>0.965</v>
+        <v>1.3511</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.6306</v>
+        <v>-0.4382</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9518</v>
+        <v>0.3616</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6788</v>
+        <v>-0.7998</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.9421</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.699</v>
+        <v>-2.9042</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3311</v>
+        <v>0.1696</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.3679</v>
+        <v>-3.0738</v>
       </c>
       <c r="G18" t="n">
         <v>-2.0618</v>
@@ -1858,13 +1858,13 @@
         <v>1.9301</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.209</v>
+        <v>-1.4142</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9822</v>
+        <v>-0.4815</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.2268</v>
+        <v>-0.9327</v>
       </c>
       <c r="V18" t="n">
         <v>0.5717</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.1263</v>
+        <v>-3.3655</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4995</v>
+        <v>-0.8986</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.6268</v>
+        <v>-2.4669</v>
       </c>
       <c r="G19" t="n">
         <v>-4.1261</v>
@@ -1936,13 +1936,13 @@
         <v>2.7021</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.0002</v>
+        <v>-1.2394</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1607</v>
+        <v>-0.5598</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8395</v>
+        <v>-0.6795</v>
       </c>
       <c r="V19" t="n">
         <v>1.228</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.5322</v>
+        <v>-5.2185</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.8309</v>
+        <v>-5.7308</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2987</v>
+        <v>0.5122</v>
       </c>
       <c r="G20" t="n">
         <v>-2.5128</v>
@@ -2014,13 +2014,13 @@
         <v>2.1231</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2823</v>
+        <v>-0.9687</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.612</v>
+        <v>-0.5119</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6703</v>
+        <v>-0.4568</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.8211</v>
+        <v>-6.9302</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.2161</v>
+        <v>-5.2175</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.605</v>
+        <v>-1.7127</v>
       </c>
       <c r="G21" t="n">
         <v>-6.2996</v>
@@ -2092,13 +2092,13 @@
         <v>2.3161</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0925</v>
+        <v>-1.0166</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5302</v>
+        <v>-0.4712</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4376</v>
+        <v>-0.5454</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-22.1049</v>
+        <v>-20.7697</v>
       </c>
       <c r="E22" t="n">
         <v>-12.0229</v>
       </c>
       <c r="F22" t="n">
-        <v>-10.082</v>
+        <v>-8.746699999999999</v>
       </c>
       <c r="G22" t="n">
         <v>-16.4167</v>
@@ -2143,10 +2143,10 @@
         <v>-7.536599999999998</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9701000000000004</v>
+        <v>-0.9701</v>
       </c>
       <c r="K22" t="n">
-        <v>3.574699999999999</v>
+        <v>3.5747</v>
       </c>
       <c r="L22" t="n">
         <v>-4.5445</v>
@@ -2161,7 +2161,7 @@
         <v>-2.992</v>
       </c>
       <c r="P22" t="n">
-        <v>-9.999999999987796e-05</v>
+        <v>-0.0001000000000001</v>
       </c>
       <c r="Q22" t="n">
         <v>-15.4407</v>
@@ -2170,13 +2170,13 @@
         <v>15.4407</v>
       </c>
       <c r="S22" t="n">
-        <v>-8.758100000000001</v>
+        <v>-7.4229</v>
       </c>
       <c r="T22" t="n">
         <v>-3.5095</v>
       </c>
       <c r="U22" t="n">
-        <v>-5.2484</v>
+        <v>-3.9133</v>
       </c>
       <c r="V22" t="n">
         <v>3.0699</v>
